--- a/gd/excel/complex_showcase.xlsx
+++ b/gd/excel/complex_showcase.xlsx
@@ -1004,62 +1004,232 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Id
-int64</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF8A5A00"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int64</t>
+          </r>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Code
-int32</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Code
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Weight
-float</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Weight
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>float</t>
+          </r>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>PreciseValue
-double</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">PreciseValue
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>double</t>
+          </r>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>IsEnabled
-bool</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">IsEnabled
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>bool</t>
+          </r>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>DisplayName
-string</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">DisplayName
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>string</t>
+          </r>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Rarity
-ShowcaseRarity</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Rarity
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>ShowcaseRarity</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>ItemTypeId
-int32</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">ItemTypeId
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>SecretSeed
-int64</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">SecretSeed
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int64</t>
+          </r>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Position
-WorldPosition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Position
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF2F6B4A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>WorldPosition</t>
+          </r>
         </is>
       </c>
       <c r="K2" s="18" t="n"/>
@@ -1068,8 +1238,25 @@
       <c r="N2" s="19" t="n"/>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>Reward
-RewardDefinition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Reward
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF2F6B4A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>RewardDefinition</t>
+          </r>
         </is>
       </c>
       <c r="P2" s="18" t="n"/>
@@ -1080,20 +1267,71 @@
       <c r="U2" s="19" t="n"/>
       <c r="V2" s="8" t="inlineStr">
         <is>
-          <t>IntValues
-vector&lt;int32&gt;</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">IntValues
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF315B9A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;int32&gt;</t>
+          </r>
         </is>
       </c>
       <c r="W2" s="8" t="inlineStr">
         <is>
-          <t>LongValues
-vector&lt;int64&gt;</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">LongValues
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF315B9A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;int64&gt;</t>
+          </r>
         </is>
       </c>
       <c r="X2" s="9" t="inlineStr">
         <is>
-          <t>Ratios
-vector&lt;float&gt;[4]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Ratios
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF315B9A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;float&gt;[4]</t>
+          </r>
         </is>
       </c>
       <c r="Y2" s="18" t="n"/>
@@ -1101,36 +1339,121 @@
       <c r="AA2" s="19" t="n"/>
       <c r="AB2" s="9" t="inlineStr">
         <is>
-          <t>Precisions
-vector&lt;double&gt;[3]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Precisions
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF315B9A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;double&gt;[3]</t>
+          </r>
         </is>
       </c>
       <c r="AC2" s="18" t="n"/>
       <c r="AD2" s="19" t="n"/>
       <c r="AE2" s="8" t="inlineStr">
         <is>
-          <t>Flags
-vector&lt;bool&gt;</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Flags
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF315B9A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;bool&gt;</t>
+          </r>
         </is>
       </c>
       <c r="AF2" s="8" t="inlineStr">
         <is>
-          <t>Aliases
-vector&lt;string&gt;</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Aliases
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF315B9A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;string&gt;</t>
+          </r>
         </is>
       </c>
       <c r="AG2" s="9" t="inlineStr">
         <is>
-          <t>Rarities
-vector&lt;ShowcaseRarity&gt;[3]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Rarities
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF315B9A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;ShowcaseRarity&gt;[3]</t>
+          </r>
         </is>
       </c>
       <c r="AH2" s="18" t="n"/>
       <c r="AI2" s="19" t="n"/>
       <c r="AJ2" s="9" t="inlineStr">
         <is>
-          <t>SpawnPoints
-vector&lt;WorldPosition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">SpawnPoints
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF315B9A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;WorldPosition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AK2" s="18" t="n"/>
@@ -1144,8 +1467,25 @@
       <c r="AS2" s="19" t="n"/>
       <c r="AT2" s="22" t="inlineStr">
         <is>
-          <t>RewardTiers
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">RewardTiers
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF315B9A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AU2" s="18" t="n"/>
@@ -1331,62 +1671,232 @@
       <c r="I4" s="11" t="n"/>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>X
-WorldPosition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">X
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>WorldPosition</t>
+          </r>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>Y
-WorldPosition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Y
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>WorldPosition</t>
+          </r>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>Z
-WorldPosition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Z
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>WorldPosition</t>
+          </r>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Space
-WorldPosition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Space
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>WorldPosition</t>
+          </r>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>IsPrecise
-WorldPosition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">IsPrecise
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>WorldPosition</t>
+          </r>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Kind
-RewardDefinition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Kind
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>RewardDefinition</t>
+          </r>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>ItemIds
-RewardDefinition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">ItemIds
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>RewardDefinition</t>
+          </r>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Amounts
-RewardDefinition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Amounts
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>RewardDefinition</t>
+          </r>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>Chance
-RewardDefinition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Chance
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>RewardDefinition</t>
+          </r>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>Bounds
-RewardDefinition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Bounds
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF2F6B4A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>RewardDefinition</t>
+          </r>
         </is>
       </c>
       <c r="T4" s="18" t="n"/>
@@ -1395,70 +1905,257 @@
       <c r="W4" s="11" t="n"/>
       <c r="X4" s="12" t="inlineStr">
         <is>
-          <t>#1
-float</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#1
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>float</t>
+          </r>
         </is>
       </c>
       <c r="Y4" s="12" t="inlineStr">
         <is>
-          <t>#2
-float</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#2
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>float</t>
+          </r>
         </is>
       </c>
       <c r="Z4" s="12" t="inlineStr">
         <is>
-          <t>#3
-float</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#3
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>float</t>
+          </r>
         </is>
       </c>
       <c r="AA4" s="12" t="inlineStr">
         <is>
-          <t>#4
-float</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#4
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>float</t>
+          </r>
         </is>
       </c>
       <c r="AB4" s="12" t="inlineStr">
         <is>
-          <t>#1
-double</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#1
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>double</t>
+          </r>
         </is>
       </c>
       <c r="AC4" s="12" t="inlineStr">
         <is>
-          <t>#2
-double</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#2
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>double</t>
+          </r>
         </is>
       </c>
       <c r="AD4" s="12" t="inlineStr">
         <is>
-          <t>#3
-double</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#3
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>double</t>
+          </r>
         </is>
       </c>
       <c r="AE4" s="11" t="n"/>
       <c r="AF4" s="11" t="n"/>
       <c r="AG4" s="12" t="inlineStr">
         <is>
-          <t>#1
-ShowcaseRarity</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#1
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>ShowcaseRarity</t>
+          </r>
         </is>
       </c>
       <c r="AH4" s="12" t="inlineStr">
         <is>
-          <t>#2
-ShowcaseRarity</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#2
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>ShowcaseRarity</t>
+          </r>
         </is>
       </c>
       <c r="AI4" s="12" t="inlineStr">
         <is>
-          <t>#3
-ShowcaseRarity</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#3
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>ShowcaseRarity</t>
+          </r>
         </is>
       </c>
       <c r="AJ4" s="13" t="inlineStr">
         <is>
-          <t>#1
-double</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#1
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>double</t>
+          </r>
         </is>
       </c>
       <c r="AK4" s="18" t="n"/>
@@ -1467,8 +2164,25 @@
       <c r="AN4" s="19" t="n"/>
       <c r="AO4" s="13" t="inlineStr">
         <is>
-          <t>#2
-double</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#2
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>double</t>
+          </r>
         </is>
       </c>
       <c r="AP4" s="18" t="n"/>
@@ -1477,8 +2191,25 @@
       <c r="AS4" s="19" t="n"/>
       <c r="AT4" s="13" t="inlineStr">
         <is>
-          <t>#1
-RewardKind</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#1
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>RewardKind</t>
+          </r>
         </is>
       </c>
       <c r="AU4" s="18" t="n"/>
@@ -1489,8 +2220,25 @@
       <c r="AZ4" s="19" t="n"/>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>#2
-RewardKind</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#2
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>RewardKind</t>
+          </r>
         </is>
       </c>
       <c r="BB4" s="18" t="n"/>
@@ -1674,20 +2422,71 @@
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>Min
-RewardDefinition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Min
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>RewardDefinition</t>
+          </r>
         </is>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>Max
-RewardDefinition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Max
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>RewardDefinition</t>
+          </r>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
         <is>
-          <t>Guaranteed
-RewardDefinition</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Guaranteed
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>RewardDefinition</t>
+          </r>
         </is>
       </c>
       <c r="V6" s="11" t="n"/>
@@ -1706,124 +2505,464 @@
       <c r="AI6" s="11" t="n"/>
       <c r="AJ6" s="6" t="inlineStr">
         <is>
-          <t>X
-vector&lt;WorldPosition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">X
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;WorldPosition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AK6" s="6" t="inlineStr">
         <is>
-          <t>Y
-vector&lt;WorldPosition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Y
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;WorldPosition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AL6" s="6" t="inlineStr">
         <is>
-          <t>Z
-vector&lt;WorldPosition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Z
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;WorldPosition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AM6" s="6" t="inlineStr">
         <is>
-          <t>Space
-vector&lt;WorldPosition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Space
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;WorldPosition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AN6" s="6" t="inlineStr">
         <is>
-          <t>IsPrecise
-vector&lt;WorldPosition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">IsPrecise
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;WorldPosition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AO6" s="6" t="inlineStr">
         <is>
-          <t>X
-vector&lt;WorldPosition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">X
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;WorldPosition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AP6" s="6" t="inlineStr">
         <is>
-          <t>Y
-vector&lt;WorldPosition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Y
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;WorldPosition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AQ6" s="6" t="inlineStr">
         <is>
-          <t>Z
-vector&lt;WorldPosition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Z
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;WorldPosition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AR6" s="6" t="inlineStr">
         <is>
-          <t>Space
-vector&lt;WorldPosition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Space
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;WorldPosition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AS6" s="6" t="inlineStr">
         <is>
-          <t>IsPrecise
-vector&lt;WorldPosition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">IsPrecise
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;WorldPosition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AT6" s="6" t="inlineStr">
         <is>
-          <t>Kind
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Kind
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AU6" s="6" t="inlineStr">
         <is>
-          <t>ItemIds
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">ItemIds
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AV6" s="6" t="inlineStr">
         <is>
-          <t>Amounts
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Amounts
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AW6" s="6" t="inlineStr">
         <is>
-          <t>Chance
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Chance
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AX6" s="7" t="inlineStr">
         <is>
-          <t>Bounds
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Bounds
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF2F6B4A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AY6" s="18" t="n"/>
       <c r="AZ6" s="19" t="n"/>
       <c r="BA6" s="6" t="inlineStr">
         <is>
-          <t>Kind
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Kind
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="BB6" s="6" t="inlineStr">
         <is>
-          <t>ItemIds
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">ItemIds
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="BC6" s="6" t="inlineStr">
         <is>
-          <t>Amounts
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Amounts
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="BD6" s="6" t="inlineStr">
         <is>
-          <t>Chance
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Chance
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="BE6" s="25" t="inlineStr">
         <is>
-          <t>Bounds
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Bounds
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF2F6B4A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="BF6" s="18" t="n"/>
@@ -1966,20 +3105,71 @@
       <c r="AW8" s="16" t="n"/>
       <c r="AX8" s="6" t="inlineStr">
         <is>
-          <t>Min
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Min
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AY8" s="6" t="inlineStr">
         <is>
-          <t>Max
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Max
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="AZ8" s="6" t="inlineStr">
         <is>
-          <t>Guaranteed
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Guaranteed
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="BA8" s="16" t="n"/>
@@ -1988,20 +3178,71 @@
       <c r="BD8" s="16" t="n"/>
       <c r="BE8" s="6" t="inlineStr">
         <is>
-          <t>Min
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Min
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="BF8" s="6" t="inlineStr">
         <is>
-          <t>Max
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Max
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
       <c r="BG8" s="17" t="inlineStr">
         <is>
-          <t>Guaranteed
-vector&lt;RewardDefinition&gt;[2]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Guaranteed
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;RewardDefinition&gt;[2]</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2510,7 +3751,7 @@
         <v>1004</v>
       </c>
       <c r="B12" t="n">
-        <v>404</v>
+        <v>304</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
@@ -2799,10 +4040,7 @@
     <mergeCell ref="AC4:AC8"/>
     <mergeCell ref="AT1:BG1"/>
   </mergeCells>
-  <dataValidations count="57">
-    <dataValidation sqref="A9:A1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="int64" prompt="超过 15 位的整数请按文本输入，最终以 canonical 校验为准" type="custom">
-      <formula1>TRUE</formula1>
-    </dataValidation>
+  <dataValidations count="54">
     <dataValidation sqref="B9:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
@@ -2821,11 +4059,9 @@
     <dataValidation sqref="G9:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Common,Rare,Epic,Legendary"</formula1>
     </dataValidation>
-    <dataValidation sqref="H9:H1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="引用" prompt="目标：ItemType.Id；最终以 canonical 校验为准" type="custom">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation sqref="I9:I1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="int64" prompt="超过 15 位的整数请按文本输入，最终以 canonical 校验为准" type="custom">
-      <formula1>TRUE</formula1>
+    <dataValidation sqref="H9:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>-2147483648</formula1>
+      <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation sqref="J9:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
       <formula1>-1E+307</formula1>
@@ -2874,9 +4110,6 @@
     <dataValidation sqref="V9:V1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
-    </dataValidation>
-    <dataValidation sqref="W9:W1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="int64" prompt="超过 15 位的整数请按文本输入，最终以 canonical 校验为准" type="custom">
-      <formula1>TRUE</formula1>
     </dataValidation>
     <dataValidation sqref="X9:X1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
       <formula1>-1E+307</formula1>
